--- a/data/trans_orig/P19C03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155386</t>
+          <t>156846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>195856</t>
+          <t>198722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169360</t>
+          <t>171790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>212000</t>
+          <t>213906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>340918</t>
+          <t>336449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>402085</t>
+          <t>398226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281981</t>
+          <t>279115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>322451</t>
+          <t>320991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>326104</t>
+          <t>324198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368744</t>
+          <t>366314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>613856</t>
+          <t>617715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>675023</t>
+          <t>679492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>191899</t>
+          <t>189105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241382</t>
+          <t>243728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239228</t>
+          <t>237471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>293946</t>
+          <t>291624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>440346</t>
+          <t>438565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>521219</t>
+          <t>515312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480746</t>
+          <t>478400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>530229</t>
+          <t>533023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510280</t>
+          <t>512602</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>564998</t>
+          <t>566755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005135</t>
+          <t>1011042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1086008</t>
+          <t>1087789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172826</t>
+          <t>171217</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216864</t>
+          <t>215527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167438</t>
+          <t>167768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211377</t>
+          <t>213814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>351169</t>
+          <t>354982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>415799</t>
+          <t>418333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327184</t>
+          <t>328521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>371222</t>
+          <t>372831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373232</t>
+          <t>370795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>417171</t>
+          <t>416841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>712858</t>
+          <t>710324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>777488</t>
+          <t>773675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176255</t>
+          <t>175152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223479</t>
+          <t>222769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208256</t>
+          <t>205262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258392</t>
+          <t>258560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398130</t>
+          <t>396263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467875</t>
+          <t>462452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486209</t>
+          <t>486919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533433</t>
+          <t>534536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>555606</t>
+          <t>555438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>605742</t>
+          <t>608736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1055811</t>
+          <t>1061234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1125556</t>
+          <t>1127423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>738000</t>
+          <t>738252</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>835283</t>
+          <t>831122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>825485</t>
+          <t>832173</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>928483</t>
+          <t>926843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1595910</t>
+          <t>1600758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1728616</t>
+          <t>1731109</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1618418</t>
+          <t>1622579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1715701</t>
+          <t>1715449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1812454</t>
+          <t>1814094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1915452</t>
+          <t>1908764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3466022</t>
+          <t>3463529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3598728</t>
+          <t>3593880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145470</t>
+          <t>147115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190447</t>
+          <t>193737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150778</t>
+          <t>150101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195633</t>
+          <t>195578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310934</t>
+          <t>310080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>375188</t>
+          <t>373436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415504</t>
+          <t>412214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460481</t>
+          <t>458836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>440168</t>
+          <t>440223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485023</t>
+          <t>485700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866564</t>
+          <t>868316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>930818</t>
+          <t>931672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248310</t>
+          <t>247251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>304475</t>
+          <t>304877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244849</t>
+          <t>245588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300327</t>
+          <t>303280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>509074</t>
+          <t>503687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>589259</t>
+          <t>592540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561603</t>
+          <t>561201</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>617768</t>
+          <t>618827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597653</t>
+          <t>594700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>653131</t>
+          <t>652392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1174799</t>
+          <t>1171518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1254984</t>
+          <t>1260371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,45%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170945</t>
+          <t>171342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220060</t>
+          <t>221930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181757</t>
+          <t>180374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>233449</t>
+          <t>230478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>367136</t>
+          <t>368812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>435982</t>
+          <t>438762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415020</t>
+          <t>413150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>464135</t>
+          <t>463738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444052</t>
+          <t>447023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495744</t>
+          <t>497127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>876599</t>
+          <t>873819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>945445</t>
+          <t>943769</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209240</t>
+          <t>210598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259805</t>
+          <t>262650</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237261</t>
+          <t>234697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291906</t>
+          <t>291349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>463007</t>
+          <t>459794</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>531962</t>
+          <t>536475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544958</t>
+          <t>542113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>595523</t>
+          <t>594165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641295</t>
+          <t>641852</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>695940</t>
+          <t>698504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1206002</t>
+          <t>1201489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1274957</t>
+          <t>1278170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>819942</t>
+          <t>823239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>931331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>850603</t>
+          <t>862414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>961140</t>
+          <t>965794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1714774</t>
+          <t>1714290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1865452</t>
+          <t>1857413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1986723</t>
+          <t>1980540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2091929</t>
+          <t>2088632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2183343</t>
+          <t>2178689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2293880</t>
+          <t>2282069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4190903</t>
+          <t>4198942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4341581</t>
+          <t>4342065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134633</t>
+          <t>138002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177499</t>
+          <t>179891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121590</t>
+          <t>122557</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>161339</t>
+          <t>162529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270008</t>
+          <t>268539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>328279</t>
+          <t>327772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347494</t>
+          <t>345102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390360</t>
+          <t>386991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383024</t>
+          <t>381834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422773</t>
+          <t>421806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741077</t>
+          <t>741584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>799348</t>
+          <t>800817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,89%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189983</t>
+          <t>187950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>242267</t>
+          <t>238299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204362</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255168</t>
+          <t>255950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>409843</t>
+          <t>408301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>479570</t>
+          <t>480163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>574079</t>
+          <t>578047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>626363</t>
+          <t>628396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>611205</t>
+          <t>610423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>662011</t>
+          <t>662740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1203149</t>
+          <t>1202556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1272876</t>
+          <t>1274418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161037</t>
+          <t>160641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207041</t>
+          <t>207110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162767</t>
+          <t>161669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207218</t>
+          <t>209237</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336366</t>
+          <t>334663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>400239</t>
+          <t>399086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343319</t>
+          <t>343250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389323</t>
+          <t>389719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372520</t>
+          <t>370501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>416971</t>
+          <t>418069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>729859</t>
+          <t>731012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>793732</t>
+          <t>795435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159752</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205085</t>
+          <t>207325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172308</t>
+          <t>175280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222718</t>
+          <t>227341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>345335</t>
+          <t>344112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415337</t>
+          <t>411993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>567550</t>
+          <t>565310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612883</t>
+          <t>613268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654123</t>
+          <t>649500</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>704533</t>
+          <t>701561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1234139</t>
+          <t>1237483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1304141</t>
+          <t>1305364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>683521</t>
+          <t>692520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>780111</t>
+          <t>783155</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>707216</t>
+          <t>707993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>799085</t>
+          <t>804134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1419039</t>
+          <t>1416417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1551376</t>
+          <t>1558872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1884222</t>
+          <t>1881178</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1980812</t>
+          <t>1971813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2068230</t>
+          <t>2063181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2160099</t>
+          <t>2159322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3980272</t>
+          <t>3972776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4112609</t>
+          <t>4115231</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023 (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121799</t>
+          <t>120051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173874</t>
+          <t>170868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99837</t>
+          <t>99724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131982</t>
+          <t>131499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231844</t>
+          <t>232280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>293221</t>
+          <t>296589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437430</t>
+          <t>440436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489505</t>
+          <t>491253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>518907</t>
+          <t>519390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>551052</t>
+          <t>551165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>968972</t>
+          <t>965604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1030349</t>
+          <t>1029913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73578</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>204474</t>
+          <t>206402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146491</t>
+          <t>143453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186908</t>
+          <t>184956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204262</t>
+          <t>201810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>367143</t>
+          <t>372456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>962242</t>
+          <t>960314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1093138</t>
+          <t>1085765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>755417</t>
+          <t>757369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>795834</t>
+          <t>798872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1741897</t>
+          <t>1736584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1904778</t>
+          <t>1907230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142068</t>
+          <t>141203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>195665</t>
+          <t>195483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90116</t>
+          <t>90674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267716</t>
+          <t>270877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>231473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>433462</t>
+          <t>428507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490602</t>
+          <t>490784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544199</t>
+          <t>545064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654337</t>
+          <t>651176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>831937</t>
+          <t>831379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1174858</t>
+          <t>1179813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387311</t>
+          <t>1376847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117747</t>
+          <t>116655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>166453</t>
+          <t>165081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126143</t>
+          <t>127122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181574</t>
+          <t>180957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258435</t>
+          <t>258175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332404</t>
+          <t>332381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>722385</t>
+          <t>723757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>771091</t>
+          <t>772183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>881343</t>
+          <t>881960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>936774</t>
+          <t>935795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1619351</t>
+          <t>1619374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1693320</t>
+          <t>1693580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>466080</t>
+          <t>462873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>677159</t>
+          <t>672309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518144</t>
+          <t>520003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>714249</t>
+          <t>711757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1057834</t>
+          <t>1075093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1341274</t>
+          <t>1342961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2675966</t>
+          <t>2680816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2887045</t>
+          <t>2890252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2863935</t>
+          <t>2866427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3060040</t>
+          <t>3058181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5590035</t>
+          <t>5588348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5873475</t>
+          <t>5856216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156846</t>
+          <t>157385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198722</t>
+          <t>199305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>171790</t>
+          <t>172445</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213906</t>
+          <t>213511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>336449</t>
+          <t>342597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398226</t>
+          <t>400160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279115</t>
+          <t>278532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320991</t>
+          <t>320452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324198</t>
+          <t>324593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>366314</t>
+          <t>365659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617715</t>
+          <t>615781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>679492</t>
+          <t>673344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189105</t>
+          <t>189114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243728</t>
+          <t>241296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>237471</t>
+          <t>237723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>291624</t>
+          <t>292767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>438565</t>
+          <t>444229</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>515312</t>
+          <t>522495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478400</t>
+          <t>480832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>533023</t>
+          <t>533014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512602</t>
+          <t>511459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>566755</t>
+          <t>566503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1011042</t>
+          <t>1003859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1087789</t>
+          <t>1082125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171217</t>
+          <t>170040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215527</t>
+          <t>217434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167768</t>
+          <t>168188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>213814</t>
+          <t>212008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>354982</t>
+          <t>351885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>418333</t>
+          <t>416159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328521</t>
+          <t>326614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>372831</t>
+          <t>374008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>370795</t>
+          <t>372601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>416841</t>
+          <t>416421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>710324</t>
+          <t>712498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>773675</t>
+          <t>776772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>175152</t>
+          <t>174446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>222769</t>
+          <t>221050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205262</t>
+          <t>206296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258560</t>
+          <t>259134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>396263</t>
+          <t>398051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>462452</t>
+          <t>466648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486919</t>
+          <t>488638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>534536</t>
+          <t>535242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>555438</t>
+          <t>554864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608736</t>
+          <t>607702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1061234</t>
+          <t>1057038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1127423</t>
+          <t>1125635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>738252</t>
+          <t>736551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>831122</t>
+          <t>833872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>832173</t>
+          <t>826844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>926843</t>
+          <t>928824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1600758</t>
+          <t>1590088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1731109</t>
+          <t>1727432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1622579</t>
+          <t>1619829</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1715449</t>
+          <t>1717150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1814094</t>
+          <t>1812113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1908764</t>
+          <t>1914093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3463529</t>
+          <t>3467206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3593880</t>
+          <t>3604550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147115</t>
+          <t>149509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193737</t>
+          <t>192608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150101</t>
+          <t>150886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195578</t>
+          <t>196587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310080</t>
+          <t>309374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>373436</t>
+          <t>375645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412214</t>
+          <t>413343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458836</t>
+          <t>456442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>440223</t>
+          <t>439214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485700</t>
+          <t>484915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>868316</t>
+          <t>866107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>931672</t>
+          <t>932378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>247251</t>
+          <t>248362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>304877</t>
+          <t>305684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>245588</t>
+          <t>244448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303280</t>
+          <t>298428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>503687</t>
+          <t>505764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>592540</t>
+          <t>584558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561201</t>
+          <t>560394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>618827</t>
+          <t>617716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594700</t>
+          <t>599552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>652392</t>
+          <t>653532</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1171518</t>
+          <t>1179500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1260371</t>
+          <t>1258294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171342</t>
+          <t>172034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221930</t>
+          <t>218564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180374</t>
+          <t>179455</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230478</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>368812</t>
+          <t>367981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>438762</t>
+          <t>437717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413150</t>
+          <t>416516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>463738</t>
+          <t>463046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447023</t>
+          <t>448047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497127</t>
+          <t>498046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>873819</t>
+          <t>874864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>943769</t>
+          <t>944600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210598</t>
+          <t>210521</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262650</t>
+          <t>262078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>234697</t>
+          <t>232726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291349</t>
+          <t>291442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>459794</t>
+          <t>458119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536475</t>
+          <t>532459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>542113</t>
+          <t>542685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>594165</t>
+          <t>594242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641852</t>
+          <t>641759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698504</t>
+          <t>700475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1201489</t>
+          <t>1205505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1278170</t>
+          <t>1279845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>823239</t>
+          <t>825376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>931331</t>
+          <t>926135</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>862414</t>
+          <t>861046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>965794</t>
+          <t>965161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,47 +4102,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1683</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1785284</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1709631</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1859926</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>30,71%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1785284</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1714290</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1857413</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>28,31%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1980540</t>
+          <t>1985736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2088632</t>
+          <t>2086495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2178689</t>
+          <t>2179322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2282069</t>
+          <t>2283437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,47 +4215,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>69,31%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>4271071</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4196429</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4346724</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>70,52%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>69,29%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>72,57%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>4271071</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>4198942</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4342065</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138002</t>
+          <t>136546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179891</t>
+          <t>179853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122557</t>
+          <t>121540</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162529</t>
+          <t>163166</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>268539</t>
+          <t>266979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>327772</t>
+          <t>328397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345102</t>
+          <t>345140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386991</t>
+          <t>388447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>381834</t>
+          <t>381197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>421806</t>
+          <t>422823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741584</t>
+          <t>740959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>800817</t>
+          <t>802377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187950</t>
+          <t>188767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>238299</t>
+          <t>240135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>203633</t>
+          <t>204813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255950</t>
+          <t>257415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>408301</t>
+          <t>411944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>480163</t>
+          <t>488030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578047</t>
+          <t>576211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>628396</t>
+          <t>627579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>610423</t>
+          <t>608958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>662740</t>
+          <t>661560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1202556</t>
+          <t>1194689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1274418</t>
+          <t>1270775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160641</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207110</t>
+          <t>208095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161669</t>
+          <t>164597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>209237</t>
+          <t>207998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>334663</t>
+          <t>336214</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>399086</t>
+          <t>400345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343250</t>
+          <t>342265</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389719</t>
+          <t>389742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>370501</t>
+          <t>371740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>418069</t>
+          <t>415141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>731012</t>
+          <t>729753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>795435</t>
+          <t>793884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159367</t>
+          <t>157983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207325</t>
+          <t>203690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175280</t>
+          <t>168700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227341</t>
+          <t>222700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344112</t>
+          <t>344458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411993</t>
+          <t>412421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>565310</t>
+          <t>568945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613268</t>
+          <t>614652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>649500</t>
+          <t>654141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>701561</t>
+          <t>708141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1237483</t>
+          <t>1237055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1305364</t>
+          <t>1305018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>692520</t>
+          <t>684125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>783155</t>
+          <t>781855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>707993</t>
+          <t>707403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>804134</t>
+          <t>799371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1416417</t>
+          <t>1423747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1558872</t>
+          <t>1555652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1881178</t>
+          <t>1882478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1971813</t>
+          <t>1980208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2063181</t>
+          <t>2067944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2159322</t>
+          <t>2159912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3972776</t>
+          <t>3975996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4115231</t>
+          <t>4107901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>143481</t>
+          <t>151784</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120051</t>
+          <t>127969</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170868</t>
+          <t>181437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>116483</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99724</t>
+          <t>111195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131499</t>
+          <t>146292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>259964</t>
+          <t>279026</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232280</t>
+          <t>248219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>296589</t>
+          <t>309813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>467823</t>
+          <t>507747</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440436</t>
+          <t>478094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491253</t>
+          <t>531562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>534406</t>
+          <t>578238</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>519390</t>
+          <t>559189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>551165</t>
+          <t>594286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1002229</t>
+          <t>1085986</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>965604</t>
+          <t>1055199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1029913</t>
+          <t>1116793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>650889</t>
+          <t>705481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>650889</t>
+          <t>705481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>650889</t>
+          <t>705481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262193</t>
+          <t>1365012</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262193</t>
+          <t>1365012</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262193</t>
+          <t>1365012</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>152351</t>
+          <t>168371</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80951</t>
+          <t>145267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206402</t>
+          <t>199964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>164946</t>
+          <t>184125</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143453</t>
+          <t>163242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184956</t>
+          <t>206943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>317297</t>
+          <t>352496</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201810</t>
+          <t>319005</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372456</t>
+          <t>385863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1014365</t>
+          <t>847809</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>960314</t>
+          <t>816216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1085765</t>
+          <t>870913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>777379</t>
+          <t>863659</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>757369</t>
+          <t>840841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>798872</t>
+          <t>884542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1791743</t>
+          <t>1711468</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1736584</t>
+          <t>1678101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1907230</t>
+          <t>1744959</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>166545</t>
+          <t>184837</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141203</t>
+          <t>156973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>195483</t>
+          <t>213249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>185598</t>
+          <t>180170</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90674</t>
+          <t>160130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>270877</t>
+          <t>204777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>20,13%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>352142</t>
+          <t>365007</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231473</t>
+          <t>331964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>428507</t>
+          <t>401687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>519722</t>
+          <t>589171</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490784</t>
+          <t>560759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545064</t>
+          <t>617035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,34 +7403,34 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>736455</t>
+          <t>615175</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651176</t>
+          <t>590568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>831379</t>
+          <t>635215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>77,35%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>74,25%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>79,87%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>70,62%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1315</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1256178</t>
+          <t>1204346</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1179813</t>
+          <t>1167666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1376847</t>
+          <t>1237389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>139312</t>
+          <t>144312</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116655</t>
+          <t>120206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165081</t>
+          <t>169780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>157140</t>
+          <t>172549</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127122</t>
+          <t>152137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180957</t>
+          <t>194353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>296452</t>
+          <t>316861</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258175</t>
+          <t>287190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332381</t>
+          <t>348604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>749526</t>
+          <t>802448</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>723757</t>
+          <t>776980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>772183</t>
+          <t>826554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>905777</t>
+          <t>903621</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>881960</t>
+          <t>881817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>935795</t>
+          <t>924033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1655303</t>
+          <t>1706069</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1619374</t>
+          <t>1674326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1693580</t>
+          <t>1735740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>888838</t>
+          <t>946760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>888838</t>
+          <t>946760</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>888838</t>
+          <t>946760</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1951755</t>
+          <t>2022930</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1951755</t>
+          <t>2022930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1951755</t>
+          <t>2022930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>649304</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>462873</t>
+          <t>598651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>672309</t>
+          <t>706277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>624166</t>
+          <t>664087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>520003</t>
+          <t>626031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>711757</t>
+          <t>708473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1225855</t>
+          <t>1313391</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1075093</t>
+          <t>1248757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1342961</t>
+          <t>1387336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2751436</t>
+          <t>2747175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2680816</t>
+          <t>2690202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2890252</t>
+          <t>2797828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2954018</t>
+          <t>2960693</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2866427</t>
+          <t>2916307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3058181</t>
+          <t>2998749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5705454</t>
+          <t>5707868</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5588348</t>
+          <t>5633923</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5856216</t>
+          <t>5772502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
